--- a/business_forms/048_sewer_testing_log--business_forms.xlsx
+++ b/business_forms/048_sewer_testing_log--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manhole_inspection',_'value':_'manhole_inspection'}</t>
+          <t>manhole_inspection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manhole Inspection', 'value': 'manhole inspection'}</t>
+          <t>Manhole Inspection</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'catch_basin_inspection',_'value':_'catch_basin_inspection'}</t>
+          <t>catch_basin_inspection</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Catch Basin Inspection', 'value': 'catch basin inspection'}</t>
+          <t>Catch Basin Inspection</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'catch_basin_cleaning',_'value':_'catch_basin_cleaning'}</t>
+          <t>catch_basin_cleaning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Catch Basin Cleaning', 'value': 'catch basin cleaning'}</t>
+          <t>Catch Basin Cleaning</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'passed',_'value':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Passed', 'value': 'passed'}</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'failed',_'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Failed', 'value': 'failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress', 'value': 'in progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
